--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -10529,42 +10529,34 @@
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>19132600</v>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>35235</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L160" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K160" s="5" t="n">
+        <v>19132600</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>35235</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
@@ -10573,7 +10565,7 @@
       </c>
       <c r="N160" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19768,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -19786,7 +19778,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21203,12 +21195,12 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>C | 542呎 (2房)
-招标单位
--
-(在售)</t>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 543呎 (2房)
+$1913万
+$35,235/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">

--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -11711,38 +11711,30 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H179" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I179" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="n">
+        <v>18095000</v>
+      </c>
+      <c r="I179" s="5" t="n">
+        <v>32900</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K179" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L179" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K179" s="5" t="n">
+        <v>18095000</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>32900</v>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
@@ -11751,7 +11743,7 @@
       </c>
       <c r="N179" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12285,38 +12277,30 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H188" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I188" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="I188" s="5" t="n">
+        <v>32000</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K188" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L188" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K188" s="5" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>32000</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
@@ -12325,7 +12309,7 @@
       </c>
       <c r="N188" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19768,7 +19752,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -19778,7 +19762,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -21345,12 +21329,12 @@
 (25年-11月-11日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
+$1810万
+$32,900/呎
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -21424,12 +21408,12 @@
 (25年-10月-16日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 550呎 (2房)
-招标单位
--
-(在售)</t>
+$1760万
+$32,000/呎
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">

--- a/files/九龙-启德-The Henley II.xlsx
+++ b/files/九龙-启德-The Henley II.xlsx
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>21080000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>36789</v>
+        <v>36661</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>21080000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>36789</v>
+        <v>36661</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>15689200</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>27381</v>
+        <v>27286</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>15689200</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>27381</v>
+        <v>27286</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>15327200</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>31998</v>
+        <v>32200</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>15327200</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>31998</v>
+        <v>32200</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>19078400</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>35135</v>
+        <v>35200</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>19078400</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>35135</v>
+        <v>35200</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>15232000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>31800</v>
+        <v>32000</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>15232000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>31800</v>
+        <v>32000</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>18861600</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>34736</v>
+        <v>34800</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>18861600</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>34736</v>
+        <v>34800</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>15525220</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>32412</v>
+        <v>32616</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>15525220</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>32412</v>
+        <v>32616</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>18728000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>34490</v>
+        <v>34554</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>18728000</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>34490</v>
+        <v>34554</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>15183800</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>26499</v>
+        <v>26407</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>15183800</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>26499</v>
+        <v>26407</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>15057500</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>31435</v>
+        <v>31633</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>15057500</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>31435</v>
+        <v>31633</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>18657000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>34359</v>
+        <v>34423</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>18657000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>34359</v>
+        <v>34423</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>15459800</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>26980</v>
+        <v>26887</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>15459800</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>26980</v>
+        <v>26887</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>15805000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>32996</v>
+        <v>33204</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>15805000</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>32996</v>
+        <v>33204</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>19582000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>36063</v>
+        <v>36129</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>19582000</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>36063</v>
+        <v>36129</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>15574100</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>27180</v>
+        <v>27085</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>15574100</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>27180</v>
+        <v>27085</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>14971000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>31255</v>
+        <v>31452</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>14971000</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>31255</v>
+        <v>31452</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>15529000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>27101</v>
+        <v>27007</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>15529000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>27101</v>
+        <v>27007</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>14927300</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>31163</v>
+        <v>31360</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>14927300</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>31163</v>
+        <v>31360</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>18495500</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>34062</v>
+        <v>34125</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>18495500</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>34062</v>
+        <v>34125</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>13828000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>24133</v>
+        <v>24049</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>13828000</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>24133</v>
+        <v>24049</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>14884600</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>31074</v>
+        <v>31270</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>14884600</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>31074</v>
+        <v>31270</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>18441400</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>33962</v>
+        <v>34025</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>18441400</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>33962</v>
+        <v>34025</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>15465700</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>32287</v>
+        <v>32491</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>15465700</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>32287</v>
+        <v>32491</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>18387200</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>33862</v>
+        <v>33925</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>18387200</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>33862</v>
+        <v>33925</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>14923500</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>26045</v>
+        <v>25954</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>14923500</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>26045</v>
+        <v>25954</v>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>14797200</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>30892</v>
+        <v>31087</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>14797200</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>30892</v>
+        <v>31087</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>18333100</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>33763</v>
+        <v>33825</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>18333100</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>33763</v>
+        <v>33825</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>15193100</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>26515</v>
+        <v>26423</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>15193100</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>26515</v>
+        <v>26423</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>19048500</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>35080</v>
+        <v>35145</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>19048500</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>35080</v>
+        <v>35145</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>15572000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>27176</v>
+        <v>27082</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>15572000</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>27176</v>
+        <v>27082</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>14667000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>30620</v>
+        <v>30813</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>14667000</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>30620</v>
+        <v>30813</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>18170600</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>33463</v>
+        <v>33525</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>18170600</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>33463</v>
+        <v>33525</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>15526000</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>27096</v>
+        <v>27002</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>15526000</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>27096</v>
+        <v>27002</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>14623300</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>30529</v>
+        <v>30721</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>14623300</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>30529</v>
+        <v>30721</v>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>18116500</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>33364</v>
+        <v>33425</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>18116500</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>33364</v>
+        <v>33425</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>14580600</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>30440</v>
+        <v>30632</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>14580600</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>30440</v>
+        <v>30632</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>18063300</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>33266</v>
+        <v>33327</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>18063300</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>33266</v>
+        <v>33327</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>14969500</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>26125</v>
+        <v>26034</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>14969500</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>26125</v>
+        <v>26034</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>15148900</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>31626</v>
+        <v>31825</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>15148900</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>31626</v>
+        <v>31825</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>18009100</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>33166</v>
+        <v>33227</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>18009100</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>33166</v>
+        <v>33227</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>14645700</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>30576</v>
+        <v>30768</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>14645700</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>30576</v>
+        <v>30768</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>17955000</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>33066</v>
+        <v>33127</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>17955000</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>33066</v>
+        <v>33127</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>14470400</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>30210</v>
+        <v>30400</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>14470400</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>30210</v>
+        <v>30400</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>19132600</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>35235</v>
+        <v>35300</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>19132600</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>35235</v>
+        <v>35300</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>14428000</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>30121</v>
+        <v>30311</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>14428000</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>30121</v>
+        <v>30311</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>17420000</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>32081</v>
+        <v>32140</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>17420000</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>32081</v>
+        <v>32140</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>14794400</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>25819</v>
+        <v>25729</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>14794400</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>25819</v>
+        <v>25729</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>14375200</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>30011</v>
+        <v>30200</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>14375200</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>30011</v>
+        <v>30200</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>18080000</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>33297</v>
+        <v>33358</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>18080000</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>33297</v>
+        <v>33358</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>13280000</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>23176</v>
+        <v>23096</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>13280000</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>23176</v>
+        <v>23096</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>14613200</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>30508</v>
+        <v>30700</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>14613200</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>30508</v>
+        <v>30700</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>15053900</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>26272</v>
+        <v>26181</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>15053900</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>26272</v>
+        <v>26181</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>14402900</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>25136</v>
+        <v>25049</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>14402900</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>25136</v>
+        <v>25049</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>17723400</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>32640</v>
+        <v>32700</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>17723400</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>32640</v>
+        <v>32700</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>14359200</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>25060</v>
+        <v>24973</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>14359200</v>
       </c>
       <c r="L212" s="5" t="n">
-        <v>25060</v>
+        <v>24973</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>17669200</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>32540</v>
+        <v>32600</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>17669200</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>32540</v>
+        <v>32600</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>14974800</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>26134</v>
+        <v>26043</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>14974800</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>26134</v>
+        <v>26043</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>17886000</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>32939</v>
+        <v>33000</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>17886000</v>
       </c>
       <c r="L223" s="5" t="n">
-        <v>32939</v>
+        <v>33000</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="E239" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>14629200</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>25531</v>
+        <v>25442</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>14629200</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>25531</v>
+        <v>25442</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>17289800</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>31841</v>
+        <v>31900</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>17289800</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>31841</v>
+        <v>31900</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>14629200</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>25531</v>
+        <v>25442</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>14629200</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>25531</v>
+        <v>25442</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>17560800</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>32340</v>
+        <v>32400</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>17560800</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>32340</v>
+        <v>32400</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>14000000</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>24433</v>
+        <v>24348</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>14000000</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>24433</v>
+        <v>24348</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         </is>
       </c>
       <c r="E259" s="4" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>17040000</v>
       </c>
       <c r="I259" s="5" t="n">
-        <v>31381</v>
+        <v>31439</v>
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>17040000</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>31381</v>
+        <v>31439</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         </is>
       </c>
       <c r="E266" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>14450000</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>25218</v>
+        <v>25130</v>
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>14450000</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>25218</v>
+        <v>25130</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         </is>
       </c>
       <c r="E275" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>14316300</v>
       </c>
       <c r="I275" s="5" t="n">
-        <v>24985</v>
+        <v>24898</v>
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>14316300</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>24985</v>
+        <v>24898</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="E284" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>13694200</v>
       </c>
       <c r="I284" s="5" t="n">
-        <v>23899</v>
+        <v>23816</v>
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>13694200</v>
       </c>
       <c r="L284" s="5" t="n">
-        <v>23899</v>
+        <v>23816</v>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         </is>
       </c>
       <c r="E293" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>13895200</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>24250</v>
+        <v>24166</v>
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>13895200</v>
       </c>
       <c r="L293" s="5" t="n">
-        <v>24250</v>
+        <v>24166</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         </is>
       </c>
       <c r="E302" s="4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>13763300</v>
       </c>
       <c r="I302" s="5" t="n">
-        <v>24020</v>
+        <v>23936</v>
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>13763300</v>
       </c>
       <c r="L302" s="5" t="n">
-        <v>24020</v>
+        <v>23936</v>
       </c>
       <c r="M302" s="3" t="inlineStr">
         <is>
@@ -19854,9 +19854,9 @@
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $2108万
-$36,789/呎
+$36,661/呎
 (22年-11月-08日)</t>
         </is>
       </c>
@@ -19917,25 +19917,25 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1908万
-$35,135/呎
+$35,200/呎
 (25年-11月-21日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1533万
-$31,998/呎
+$32,200/呎
 (25年-05月-28日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1569万
-$27,381/呎
+$27,286/呎
 (23年-06月-23日)</t>
         </is>
       </c>
@@ -19996,17 +19996,17 @@
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1886万
-$34,736/呎
+$34,800/呎
 (25年-08月-29日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1523万
-$31,800/呎
+$32,000/呎
 (26年-06月-23日)</t>
         </is>
       </c>
@@ -20075,17 +20075,17 @@
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1873万
-$34,490/呎
+$34,554/呎
 (25年-08月-29日)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1553万
-$32,412/呎
+$32,616/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -20154,25 +20154,25 @@
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1866万
-$34,359/呎
+$34,423/呎
 (23年-06月-12日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1506万
-$31,435/呎
+$31,633/呎
 (25年-02月-06日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1518万
-$26,499/呎
+$26,407/呎
 (22年-07月-25日)</t>
         </is>
       </c>
@@ -20233,25 +20233,25 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1958万
-$36,063/呎
+$36,129/呎
 (22年-10月-27日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1580万
-$32,996/呎
+$33,204/呎
 (22年-09月-05日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1546万
-$26,980/呎
+$26,887/呎
 (22年-07月-28日)</t>
         </is>
       </c>
@@ -20320,17 +20320,17 @@
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1497万
-$31,255/呎
+$31,452/呎
 (23年-01月-10日)</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1557万
-$27,180/呎
+$27,085/呎
 (22年-08月-01日)</t>
         </is>
       </c>
@@ -20391,25 +20391,25 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1850万
-$34,062/呎
+$34,125/呎
 (23年-04月-20日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1493万
-$31,163/呎
+$31,360/呎
 (23年-03月-21日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1553万
-$27,101/呎
+$27,007/呎
 (22年-08月-03日)</t>
         </is>
       </c>
@@ -20470,25 +20470,25 @@
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1844万
-$33,962/呎
+$34,025/呎
 (23年-06月-29日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1488万
-$31,074/呎
+$31,270/呎
 (24年-04月-16日)</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1383万
-$24,133/呎
+$24,049/呎
 (25年-04月-23日)</t>
         </is>
       </c>
@@ -20549,17 +20549,17 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1839万
-$33,862/呎
+$33,925/呎
 (23年-08月-29日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1547万
-$32,287/呎
+$32,491/呎
 (24年-04月-10日)</t>
         </is>
       </c>
@@ -20628,25 +20628,25 @@
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1833万
-$33,763/呎
+$33,825/呎
 (25年-02月-10日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1480万
-$30,892/呎
+$31,087/呎
 (25年-01月-20日)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1492万
-$26,045/呎
+$25,954/呎
 (22年-08月-09日)</t>
         </is>
       </c>
@@ -20707,9 +20707,9 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1905万
-$35,080/呎
+$35,145/呎
 (22年-09月-16日)</t>
         </is>
       </c>
@@ -20723,9 +20723,9 @@
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1519万
-$26,515/呎
+$26,423/呎
 (22年-08月-15日)</t>
         </is>
       </c>
@@ -20786,25 +20786,25 @@
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1817万
-$33,463/呎
+$33,525/呎
 (26年-02月-16日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1467万
-$30,620/呎
+$30,813/呎
 (24年-05月-17日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1557万
-$27,176/呎
+$27,082/呎
 (22年-08月-15日)</t>
         </is>
       </c>
@@ -20865,25 +20865,25 @@
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1812万
-$33,364/呎
+$33,425/呎
 (25年-05月-21日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1462万
-$30,529/呎
+$30,721/呎
 (23年-08月-14日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1553万
-$27,096/呎
+$27,002/呎
 (22年-08月-08日)</t>
         </is>
       </c>
@@ -20944,17 +20944,17 @@
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1806万
-$33,266/呎
+$33,327/呎
 (23年-06月-12日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1458万
-$30,440/呎
+$30,632/呎
 (23年-02月-10日)</t>
         </is>
       </c>
@@ -21023,25 +21023,25 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1801万
-$33,166/呎
+$33,227/呎
 (25年-12月-30日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1515万
-$31,626/呎
+$31,825/呎
 (23年-08月-03日)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1497万
-$26,125/呎
+$26,034/呎
 (22年-08月-05日)</t>
         </is>
       </c>
@@ -21102,17 +21102,17 @@
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1796万
-$33,066/呎
+$33,127/呎
 (26年-02月-10日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1465万
-$30,576/呎
+$30,768/呎
 (23年-12月-29日)</t>
         </is>
       </c>
@@ -21181,17 +21181,17 @@
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1913万
-$35,235/呎
+$35,300/呎
 (26年-09月-28日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1447万
-$30,210/呎
+$30,400/呎
 (26年-04月-30日)</t>
         </is>
       </c>
@@ -21260,17 +21260,17 @@
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1742万
-$32,081/呎
+$32,140/呎
 (26年-04月-14日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1443万
-$30,121/呎
+$30,311/呎
 (25年-11月-28日)</t>
         </is>
       </c>
@@ -21339,25 +21339,25 @@
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1808万
-$33,297/呎
+$33,358/呎
 (26年-08月-03日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1438万
-$30,011/呎
+$30,200/呎
 (26年-04月-28日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1479万
-$25,819/呎
+$25,729/呎
 (22年-08月-23日)</t>
         </is>
       </c>
@@ -21426,17 +21426,17 @@
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>D | 479呎 (2房)
+          <t>D | 476呎 (2房)
 $1461万
-$30,508/呎
+$30,700/呎
 (26年-08月-18日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1328万
-$23,176/呎
+$23,096/呎
 (25年-05月-02日)</t>
         </is>
       </c>
@@ -21513,9 +21513,9 @@
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1505万
-$26,272/呎
+$26,181/呎
 (22年-08月-25日)</t>
         </is>
       </c>
@@ -21576,9 +21576,9 @@
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1772万
-$32,640/呎
+$32,700/呎
 (26年-04月-24日)</t>
         </is>
       </c>
@@ -21592,9 +21592,9 @@
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1440万
-$25,136/呎
+$25,049/呎
 (22年-08月-29日)</t>
         </is>
       </c>
@@ -21655,9 +21655,9 @@
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1767万
-$32,540/呎
+$32,600/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -21671,9 +21671,9 @@
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1436万
-$25,060/呎
+$24,973/呎
 (22年-09月-13日)</t>
         </is>
       </c>
@@ -21734,9 +21734,9 @@
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1789万
-$32,939/呎
+$33,000/呎
 (26年-07月-09日)</t>
         </is>
       </c>
@@ -21750,9 +21750,9 @@
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1497万
-$26,134/呎
+$26,043/呎
 (22年-10月-27日)</t>
         </is>
       </c>
@@ -21892,9 +21892,9 @@
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1729万
-$31,841/呎
+$31,900/呎
 (26年-04月-10日)</t>
         </is>
       </c>
@@ -21908,9 +21908,9 @@
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1463万
-$25,531/呎
+$25,442/呎
 (22年-09月-15日)</t>
         </is>
       </c>
@@ -21971,9 +21971,9 @@
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1756万
-$32,340/呎
+$32,400/呎
 (26年-07月-14日)</t>
         </is>
       </c>
@@ -21987,9 +21987,9 @@
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1463万
-$25,531/呎
+$25,442/呎
 (22年-09月-22日)</t>
         </is>
       </c>
@@ -22050,9 +22050,9 @@
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>C | 543呎 (2房)
+          <t>C | 542呎 (2房)
 $1704万
-$31,381/呎
+$31,439/呎
 (26年-07月-14日)</t>
         </is>
       </c>
@@ -22066,9 +22066,9 @@
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1400万
-$24,433/呎
+$24,348/呎
 (26年-04月-17日)</t>
         </is>
       </c>
@@ -22145,9 +22145,9 @@
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1445万
-$25,218/呎
+$25,130/呎
 (22年-09月-29日)</t>
         </is>
       </c>
@@ -22224,9 +22224,9 @@
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1432万
-$24,985/呎
+$24,898/呎
 (22年-10月-20日)</t>
         </is>
       </c>
@@ -22303,9 +22303,9 @@
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1369万
-$23,899/呎
+$23,816/呎
 (23年-01月-09日)</t>
         </is>
       </c>
@@ -22382,9 +22382,9 @@
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1390万
-$24,250/呎
+$24,166/呎
 (22年-08月-17日)</t>
         </is>
       </c>
@@ -22440,9 +22440,9 @@
       </c>
       <c r="F38" s="23" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 575呎 (2房)
 $1376万
-$24,020/呎
+$23,936/呎
 (23年-02月-17日)</t>
         </is>
       </c>
